--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2021_metropolitana_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2021_metropolitana_provincial.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 11:27</t>
+    <t xml:space="preserve">2026-09-09 19:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2021_metropolitana_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2021_metropolitana_provincial.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:04</t>
+    <t xml:space="preserve">2026-09-17 04:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2021_metropolitana_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2021_metropolitana_provincial.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 04:21</t>
+    <t xml:space="preserve">2026-09-25 11:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2021_metropolitana_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2021_metropolitana_provincial.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25 11:15</t>
+    <t xml:space="preserve">2026-09-26 23:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2021_metropolitana_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2021_metropolitana_provincial.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-26 23:49</t>
+    <t xml:space="preserve">2026-10-05 04:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
